--- a/docs/데이터 정의서.xlsx
+++ b/docs/데이터 정의서.xlsx
@@ -1746,19 +1746,17 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="A7" s="3"/>
+      <c r="B7" s="4"/>
     </row>
     <row r="8" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>11</v>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>요구사항정의서.xlsx, RAG 구현 명세.md</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -1787,8 +1785,10 @@
       </c>
     </row>
     <row r="15" spans="1:2" ht="33" x14ac:dyDescent="0.3">
-      <c r="B15" s="4" t="s">
-        <v>17</v>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>5) RAG_문서 / RAG_API : 근거 문단 필드와 상담 API 계약</t>
+        </is>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -1797,13 +1797,17 @@
       </c>
     </row>
     <row r="18" spans="1:2" ht="24" x14ac:dyDescent="0.3">
-      <c r="B18" s="6" t="s">
-        <v>19</v>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>- CSV 3종의 항목 정의와 RAG 문서·API 계약을 정리합니다.</t>
+        </is>
       </c>
     </row>
     <row r="19" spans="1:2" ht="24" x14ac:dyDescent="0.3">
-      <c r="B19" s="6" t="s">
-        <v>20</v>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>- 사용자 데이터는 미수집 상태이며, RAG 첫 버전의 구현 범위에서 제외합니다.</t>
+        </is>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -1935,8 +1939,10 @@
       <c r="D5" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>50</v>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>미수집 · 항목 미정</t>
+        </is>
       </c>
       <c r="F5" s="8" t="s">
         <v>51</v>
@@ -3046,8 +3052,10 @@
       <c r="B13" s="20" t="str">
         <v>JSON / 파일</v>
       </c>
-      <c r="C13" s="20" t="str">
-        <v>수업 결정</v>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>구현 결정</t>
+        </is>
       </c>
       <c r="D13" s="20" t="str">
         <v>project/data/reference/</v>
@@ -3055,8 +3063,10 @@
       <c r="E13" s="20" t="str">
         <v>SQLite 상품 DB 유지. 새 DB·벡터DB 설치는 필수 아님.</v>
       </c>
-      <c r="F13" s="20" t="str">
-        <v>실습 보완 명세.md 참조</v>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>RAG 구현 명세.md 참조</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3235,8 +3245,10 @@
       <c r="E8" s="20" t="str">
         <v>파싱·검증 실패는 unavailable</v>
       </c>
-      <c r="F8" s="20" t="str">
-        <v>실습 보완 명세.md 참조</v>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>RAG 구현 명세.md 참조</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
